--- a/StructureDefinition-openimis-coverage-eligibility-request.xlsx
+++ b/StructureDefinition-openimis-coverage-eligibility-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8068,7 +8068,7 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>22</v>
@@ -9088,7 +9088,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>22</v>
@@ -9316,7 +9316,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>22</v>
@@ -9430,7 +9430,7 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>22</v>
@@ -9660,7 +9660,7 @@
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>22</v>
@@ -9774,7 +9774,7 @@
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>22</v>
@@ -10576,7 +10576,7 @@
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>22</v>
@@ -11832,7 +11832,7 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>22</v>
@@ -12402,7 +12402,7 @@
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>22</v>
@@ -12634,7 +12634,7 @@
         <v>79</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>22</v>
@@ -12750,7 +12750,7 @@
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>22</v>
@@ -12864,7 +12864,7 @@
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>22</v>
@@ -12978,7 +12978,7 @@
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>22</v>
@@ -13092,7 +13092,7 @@
         <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>22</v>
@@ -13206,7 +13206,7 @@
         <v>79</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>22</v>
@@ -13776,7 +13776,7 @@
         <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>22</v>
@@ -14348,7 +14348,7 @@
         <v>79</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>22</v>
@@ -16176,7 +16176,7 @@
         <v>79</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>22</v>
@@ -16408,7 +16408,7 @@
         <v>79</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>22</v>
@@ -16524,7 +16524,7 @@
         <v>79</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>22</v>
@@ -16638,7 +16638,7 @@
         <v>79</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>22</v>
@@ -16752,7 +16752,7 @@
         <v>79</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>22</v>
@@ -16866,7 +16866,7 @@
         <v>79</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>22</v>
@@ -16980,7 +16980,7 @@
         <v>79</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>22</v>
@@ -17550,7 +17550,7 @@
         <v>79</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>22</v>
@@ -18122,7 +18122,7 @@
         <v>79</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>22</v>
@@ -19950,7 +19950,7 @@
         <v>79</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>22</v>
@@ -20182,7 +20182,7 @@
         <v>79</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>22</v>
@@ -20298,7 +20298,7 @@
         <v>79</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>22</v>
@@ -20412,7 +20412,7 @@
         <v>79</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>22</v>
@@ -20526,7 +20526,7 @@
         <v>79</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>22</v>
@@ -20640,7 +20640,7 @@
         <v>79</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>22</v>
@@ -20754,7 +20754,7 @@
         <v>79</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>22</v>
@@ -21324,7 +21324,7 @@
         <v>79</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-coverage-eligibility-request.xlsx
+++ b/StructureDefinition-openimis-coverage-eligibility-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-coverage-eligibility-request.xlsx
+++ b/StructureDefinition-openimis-coverage-eligibility-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
